--- a/metadata/Data 2023 For Syl Segmentation_2.xlsx
+++ b/metadata/Data 2023 For Syl Segmentation_2.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -569,7 +569,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -607,7 +607,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -759,7 +759,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -873,7 +873,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -987,7 +987,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F321" t="n">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F322" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F323" t="n">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F337" t="n">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F339" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F346" t="n">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F347" t="n">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F348" t="n">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F349" t="n">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F351" t="n">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F352" t="n">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F357" t="n">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F358" t="n">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F359" t="n">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F360" t="n">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F361" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F362" t="n">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F363" t="n">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F364" t="n">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F365" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F366" t="n">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F367" t="n">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F368" t="n">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F382" t="n">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F383" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F384" t="n">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F385" t="n">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F386" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F387" t="n">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F388" t="n">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F389" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F390" t="n">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F391" t="n">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F392" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F393" t="n">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F399" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F400" t="n">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F401" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F402" t="n">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F403" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F404" t="n">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F405" t="n">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F406" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F407" t="n">
@@ -25345,7 +25345,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F656" t="n">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F657" t="n">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F658" t="n">
@@ -25459,7 +25459,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F659" t="n">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F660" t="n">
@@ -25535,7 +25535,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -25649,7 +25649,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -25877,7 +25877,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F670" t="n">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F672" t="n">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -26105,7 +26105,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -26143,7 +26143,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F679" t="n">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F680" t="n">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -26371,7 +26371,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F683" t="n">
@@ -26409,7 +26409,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F686" t="n">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -26599,7 +26599,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F689" t="n">
@@ -26637,7 +26637,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -26675,7 +26675,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F691" t="n">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F692" t="n">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F693" t="n">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F694" t="n">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F695" t="n">
@@ -26865,7 +26865,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F696" t="n">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F697" t="n">
@@ -26941,7 +26941,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F698" t="n">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F699" t="n">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F700" t="n">
@@ -27055,7 +27055,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F701" t="n">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F702" t="n">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F703" t="n">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F704" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F705" t="n">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F706" t="n">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F707" t="n">
@@ -27321,7 +27321,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F708" t="n">
@@ -27359,7 +27359,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F709" t="n">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F710" t="n">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F711" t="n">
@@ -27473,7 +27473,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F712" t="n">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F713" t="n">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F714" t="n">
@@ -27587,7 +27587,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F715" t="n">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F716" t="n">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F717" t="n">
@@ -27701,7 +27701,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F718" t="n">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F719" t="n">
@@ -27777,7 +27777,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F720" t="n">
@@ -27815,7 +27815,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F721" t="n">
@@ -27853,7 +27853,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F722" t="n">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F723" t="n">
@@ -27929,7 +27929,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F724" t="n">
@@ -27967,7 +27967,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F725" t="n">
@@ -28005,7 +28005,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F726" t="n">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F727" t="n">
@@ -28081,7 +28081,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F728" t="n">
@@ -28119,7 +28119,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F729" t="n">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F730" t="n">
@@ -28195,7 +28195,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F731" t="n">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F732" t="n">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F733" t="n">
@@ -28309,7 +28309,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F734" t="n">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F735" t="n">
@@ -28385,7 +28385,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F736" t="n">
@@ -28423,7 +28423,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F737" t="n">
@@ -28461,7 +28461,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F738" t="n">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F739" t="n">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F740" t="n">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F741" t="n">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F742" t="n">
@@ -28651,7 +28651,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F743" t="n">
@@ -28689,7 +28689,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F744" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F745" t="n">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F746" t="n">
@@ -28803,7 +28803,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F747" t="n">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F748" t="n">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F749" t="n">
@@ -28917,7 +28917,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F750" t="n">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F751" t="n">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F752" t="n">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F753" t="n">
@@ -29069,7 +29069,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F754" t="n">
@@ -29107,7 +29107,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F755" t="n">
@@ -29145,7 +29145,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F756" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -29221,7 +29221,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F758" t="n">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F759" t="n">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F760" t="n">
@@ -29335,7 +29335,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F761" t="n">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F762" t="n">
@@ -29411,7 +29411,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F763" t="n">
@@ -29449,7 +29449,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F764" t="n">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F765" t="n">
@@ -29525,7 +29525,7 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F766" t="n">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F767" t="n">
@@ -29601,7 +29601,7 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F768" t="n">
@@ -29639,7 +29639,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F769" t="n">
@@ -29677,7 +29677,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F770" t="n">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F772" t="n">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F773" t="n">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F774" t="n">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F775" t="n">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F776" t="n">
@@ -29943,7 +29943,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F777" t="n">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F778" t="n">
@@ -30019,7 +30019,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F779" t="n">
@@ -30057,7 +30057,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F780" t="n">
@@ -30095,7 +30095,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F781" t="n">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F782" t="n">
@@ -30171,7 +30171,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F783" t="n">
@@ -30209,7 +30209,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F784" t="n">
@@ -30247,7 +30247,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F785" t="n">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F786" t="n">
@@ -30323,7 +30323,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F787" t="n">
@@ -30361,7 +30361,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F788" t="n">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F789" t="n">
@@ -30437,7 +30437,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F790" t="n">
@@ -30475,7 +30475,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F791" t="n">
@@ -30513,7 +30513,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F792" t="n">
@@ -30551,7 +30551,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F793" t="n">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F794" t="n">
@@ -30627,7 +30627,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F795" t="n">
@@ -30665,7 +30665,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F796" t="n">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F797" t="n">
@@ -30741,7 +30741,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F798" t="n">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F799" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F800" t="n">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F801" t="n">
@@ -30893,7 +30893,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F802" t="n">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F803" t="n">
@@ -30969,7 +30969,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F804" t="n">
@@ -31007,7 +31007,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F805" t="n">
@@ -31045,7 +31045,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F806" t="n">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F807" t="n">
@@ -31121,7 +31121,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F808" t="n">
@@ -31159,7 +31159,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F809" t="n">
@@ -31197,7 +31197,7 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F810" t="n">
@@ -31235,7 +31235,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F811" t="n">
@@ -31273,7 +31273,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F812" t="n">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F813" t="n">
@@ -31349,7 +31349,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F814" t="n">
@@ -31387,7 +31387,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F815" t="n">
@@ -31425,7 +31425,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F816" t="n">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F817" t="n">
@@ -31501,7 +31501,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F818" t="n">
@@ -31539,7 +31539,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F819" t="n">
@@ -31577,7 +31577,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F820" t="n">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F821" t="n">
@@ -31653,7 +31653,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F822" t="n">
@@ -31691,7 +31691,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F823" t="n">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F824" t="n">
@@ -31767,7 +31767,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F825" t="n">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F826" t="n">
@@ -31843,7 +31843,7 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F827" t="n">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F828" t="n">
@@ -31919,7 +31919,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F829" t="n">
@@ -31957,7 +31957,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F830" t="n">
@@ -31995,7 +31995,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F831" t="n">
@@ -32033,7 +32033,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F832" t="n">
@@ -32071,7 +32071,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F833" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F834" t="n">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F835" t="n">
@@ -32185,7 +32185,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F836" t="n">
@@ -32223,7 +32223,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F837" t="n">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F838" t="n">
@@ -32299,7 +32299,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F839" t="n">
@@ -32337,7 +32337,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F840" t="n">
@@ -32375,7 +32375,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F841" t="n">
@@ -32413,7 +32413,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F842" t="n">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F843" t="n">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F844" t="n">
@@ -32527,7 +32527,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F845" t="n">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F846" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F847" t="n">
@@ -32641,7 +32641,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F848" t="n">
@@ -32679,7 +32679,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F849" t="n">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F850" t="n">
@@ -32755,7 +32755,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F851" t="n">
@@ -32793,7 +32793,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F852" t="n">
@@ -32831,7 +32831,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F853" t="n">
@@ -32869,7 +32869,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F854" t="n">
@@ -32907,7 +32907,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F855" t="n">
@@ -32945,7 +32945,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F856" t="n">
@@ -32983,7 +32983,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F857" t="n">
@@ -33021,7 +33021,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F858" t="n">
@@ -33059,7 +33059,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F859" t="n">
@@ -33097,7 +33097,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F860" t="n">
@@ -33135,7 +33135,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F861" t="n">
@@ -33173,7 +33173,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F862" t="n">
@@ -33211,7 +33211,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F863" t="n">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F864" t="n">
@@ -33287,7 +33287,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F865" t="n">
@@ -33325,7 +33325,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F866" t="n">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F867" t="n">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F868" t="n">
@@ -33439,7 +33439,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F869" t="n">
@@ -33477,7 +33477,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F870" t="n">
@@ -33515,7 +33515,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F871" t="n">
@@ -33553,7 +33553,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F872" t="n">
@@ -33591,7 +33591,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F873" t="n">
@@ -33629,7 +33629,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F874" t="n">
@@ -33667,7 +33667,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F875" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F876" t="n">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F877" t="n">
@@ -33781,7 +33781,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F878" t="n">
@@ -33819,7 +33819,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F879" t="n">
@@ -33857,7 +33857,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F880" t="n">
@@ -33895,7 +33895,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F881" t="n">
@@ -33933,7 +33933,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F882" t="n">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F883" t="n">
@@ -34009,7 +34009,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F884" t="n">
@@ -34047,7 +34047,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F885" t="n">
@@ -34085,7 +34085,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F886" t="n">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F887" t="n">
@@ -34161,7 +34161,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F888" t="n">
@@ -34199,7 +34199,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F889" t="n">
@@ -34237,7 +34237,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F890" t="n">
@@ -34275,7 +34275,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F891" t="n">
@@ -34313,7 +34313,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F892" t="n">
@@ -34351,7 +34351,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F893" t="n">
@@ -34389,7 +34389,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F894" t="n">
@@ -34427,7 +34427,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F895" t="n">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F896" t="n">
@@ -34503,7 +34503,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F897" t="n">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F898" t="n">
@@ -34579,7 +34579,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F899" t="n">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F900" t="n">
@@ -34655,7 +34655,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F901" t="n">
@@ -34693,7 +34693,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F902" t="n">
@@ -34731,7 +34731,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F903" t="n">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F904" t="n">
@@ -34807,7 +34807,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F905" t="n">
@@ -34845,7 +34845,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F906" t="n">
@@ -34883,7 +34883,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F907" t="n">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F908" t="n">
@@ -34959,7 +34959,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F909" t="n">
@@ -34997,7 +34997,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F910" t="n">
@@ -35035,7 +35035,7 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F911" t="n">
@@ -35073,7 +35073,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F912" t="n">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F913" t="n">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F914" t="n">
@@ -35187,7 +35187,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F915" t="n">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F916" t="n">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F917" t="n">
@@ -35301,7 +35301,7 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F918" t="n">
@@ -35339,7 +35339,7 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F919" t="n">
@@ -35377,7 +35377,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F920" t="n">
@@ -35415,7 +35415,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F921" t="n">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F922" t="n">
@@ -35491,7 +35491,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F923" t="n">
@@ -35529,7 +35529,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F924" t="n">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F925" t="n">
@@ -35605,7 +35605,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F926" t="n">
@@ -35643,7 +35643,7 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F927" t="n">
@@ -35681,7 +35681,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F928" t="n">
@@ -35719,7 +35719,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F929" t="n">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F930" t="n">
@@ -35795,7 +35795,7 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F931" t="n">
@@ -35833,7 +35833,7 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F932" t="n">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F933" t="n">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F934" t="n">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F935" t="n">
@@ -35985,7 +35985,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F936" t="n">
@@ -36023,7 +36023,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F937" t="n">
@@ -36061,7 +36061,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F938" t="n">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F939" t="n">
@@ -36137,7 +36137,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F940" t="n">
@@ -36175,7 +36175,7 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F941" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F942" t="n">
@@ -36251,7 +36251,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F943" t="n">
@@ -36289,7 +36289,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F944" t="n">
@@ -36327,7 +36327,7 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F945" t="n">
@@ -36365,7 +36365,7 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F946" t="n">
@@ -36403,7 +36403,7 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F947" t="n">
@@ -36441,7 +36441,7 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F948" t="n">
@@ -36479,7 +36479,7 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F949" t="n">
@@ -36517,7 +36517,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F950" t="n">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F951" t="n">
@@ -36593,7 +36593,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F952" t="n">
@@ -36631,7 +36631,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F953" t="n">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F954" t="n">
@@ -36707,7 +36707,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F955" t="n">
@@ -36745,7 +36745,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F956" t="n">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F957" t="n">
@@ -36821,7 +36821,7 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F958" t="n">
